--- a/artfynd/A 3922-2025 artfynd.xlsx
+++ b/artfynd/A 3922-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128702164</v>
       </c>
       <c r="B2" t="n">
-        <v>91760</v>
+        <v>91762</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128702163</v>
       </c>
       <c r="B3" t="n">
-        <v>91464</v>
+        <v>91466</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128702176</v>
       </c>
       <c r="B4" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 3922-2025 artfynd.xlsx
+++ b/artfynd/A 3922-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128702164</v>
       </c>
       <c r="B2" t="n">
-        <v>91762</v>
+        <v>91763</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128702163</v>
       </c>
       <c r="B3" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128702176</v>
       </c>
       <c r="B4" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 3922-2025 artfynd.xlsx
+++ b/artfynd/A 3922-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128702164</v>
       </c>
       <c r="B2" t="n">
-        <v>91763</v>
+        <v>91790</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128702163</v>
+        <v>128702176</v>
       </c>
       <c r="B3" t="n">
-        <v>91467</v>
+        <v>92784</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>790361</v>
+        <v>790349</v>
       </c>
       <c r="R3" t="n">
-        <v>7366948</v>
+        <v>7366898</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128702176</v>
+        <v>128702163</v>
       </c>
       <c r="B4" t="n">
-        <v>92757</v>
+        <v>91494</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>790349</v>
+        <v>790361</v>
       </c>
       <c r="R4" t="n">
-        <v>7366898</v>
+        <v>7366948</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>

--- a/artfynd/A 3922-2025 artfynd.xlsx
+++ b/artfynd/A 3922-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128702164</v>
       </c>
       <c r="B2" t="n">
-        <v>91790</v>
+        <v>91795</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128702176</v>
       </c>
       <c r="B3" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128702163</v>
       </c>
       <c r="B4" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 3922-2025 artfynd.xlsx
+++ b/artfynd/A 3922-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>128702164</v>
       </c>
       <c r="B2" t="n">
-        <v>91795</v>
+        <v>91800</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128702176</v>
+        <v>128702163</v>
       </c>
       <c r="B3" t="n">
-        <v>92789</v>
+        <v>91504</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>790349</v>
+        <v>790361</v>
       </c>
       <c r="R3" t="n">
-        <v>7366898</v>
+        <v>7366948</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128702163</v>
+        <v>128702176</v>
       </c>
       <c r="B4" t="n">
-        <v>91499</v>
+        <v>92794</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>790361</v>
+        <v>790349</v>
       </c>
       <c r="R4" t="n">
-        <v>7366948</v>
+        <v>7366898</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -963,6 +963,103 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128894588</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57876</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Norr-Lillån, Nb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>790319</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7366905</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3922-2025 artfynd.xlsx
+++ b/artfynd/A 3922-2025 artfynd.xlsx
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128702163</v>
+        <v>128702176</v>
       </c>
       <c r="B3" t="n">
-        <v>91504</v>
+        <v>92794</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>790361</v>
+        <v>790349</v>
       </c>
       <c r="R3" t="n">
-        <v>7366948</v>
+        <v>7366898</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128702176</v>
+        <v>128702163</v>
       </c>
       <c r="B4" t="n">
-        <v>92794</v>
+        <v>91504</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>790349</v>
+        <v>790361</v>
       </c>
       <c r="R4" t="n">
-        <v>7366898</v>
+        <v>7366948</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>

--- a/artfynd/A 3922-2025 artfynd.xlsx
+++ b/artfynd/A 3922-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128702164</v>
       </c>
       <c r="B2" t="n">
-        <v>91800</v>
+        <v>91804</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128702176</v>
       </c>
       <c r="B3" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128702163</v>
       </c>
       <c r="B4" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128894588</v>
       </c>
       <c r="B5" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 3922-2025 artfynd.xlsx
+++ b/artfynd/A 3922-2025 artfynd.xlsx
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128702176</v>
+        <v>128702163</v>
       </c>
       <c r="B3" t="n">
-        <v>92798</v>
+        <v>91508</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>790349</v>
+        <v>790361</v>
       </c>
       <c r="R3" t="n">
-        <v>7366898</v>
+        <v>7366948</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128702163</v>
+        <v>128702176</v>
       </c>
       <c r="B4" t="n">
-        <v>91508</v>
+        <v>92798</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>790361</v>
+        <v>790349</v>
       </c>
       <c r="R4" t="n">
-        <v>7366948</v>
+        <v>7366898</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>

--- a/artfynd/A 3922-2025 artfynd.xlsx
+++ b/artfynd/A 3922-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128702164</v>
       </c>
       <c r="B2" t="n">
-        <v>91804</v>
+        <v>91809</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128702163</v>
+        <v>128702176</v>
       </c>
       <c r="B3" t="n">
-        <v>91508</v>
+        <v>92803</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>790361</v>
+        <v>790349</v>
       </c>
       <c r="R3" t="n">
-        <v>7366948</v>
+        <v>7366898</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128702176</v>
+        <v>128702163</v>
       </c>
       <c r="B4" t="n">
-        <v>92798</v>
+        <v>91513</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>790349</v>
+        <v>790361</v>
       </c>
       <c r="R4" t="n">
-        <v>7366898</v>
+        <v>7366948</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -969,7 +969,7 @@
         <v>128894588</v>
       </c>
       <c r="B5" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 3922-2025 artfynd.xlsx
+++ b/artfynd/A 3922-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128702164</v>
       </c>
       <c r="B2" t="n">
-        <v>91805</v>
+        <v>91808</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128702163</v>
       </c>
       <c r="B3" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128702176</v>
       </c>
       <c r="B4" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 3922-2025 artfynd.xlsx
+++ b/artfynd/A 3922-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128702164</v>
       </c>
       <c r="B2" t="n">
-        <v>91808</v>
+        <v>91811</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128702163</v>
       </c>
       <c r="B3" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128702176</v>
       </c>
       <c r="B4" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 3922-2025 artfynd.xlsx
+++ b/artfynd/A 3922-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128702164</v>
       </c>
       <c r="B2" t="n">
-        <v>91811</v>
+        <v>91818</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128702163</v>
+        <v>128702176</v>
       </c>
       <c r="B3" t="n">
-        <v>91526</v>
+        <v>92826</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>790361</v>
+        <v>790349</v>
       </c>
       <c r="R3" t="n">
-        <v>7366948</v>
+        <v>7366898</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128702176</v>
+        <v>128702163</v>
       </c>
       <c r="B4" t="n">
-        <v>92819</v>
+        <v>91533</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>790349</v>
+        <v>790361</v>
       </c>
       <c r="R4" t="n">
-        <v>7366898</v>
+        <v>7366948</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -969,7 +969,7 @@
         <v>128894588</v>
       </c>
       <c r="B5" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 3922-2025 artfynd.xlsx
+++ b/artfynd/A 3922-2025 artfynd.xlsx
@@ -969,7 +969,7 @@
         <v>128894588</v>
       </c>
       <c r="B5" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 3922-2025 artfynd.xlsx
+++ b/artfynd/A 3922-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>128702164</v>
       </c>
       <c r="B2" t="n">
-        <v>91818</v>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128702176</v>
+        <v>128702165</v>
       </c>
       <c r="B3" t="n">
-        <v>92826</v>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>790349</v>
+        <v>790388</v>
       </c>
       <c r="R3" t="n">
-        <v>7366898</v>
+        <v>7366959</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -872,7 +872,7 @@
         <v>128702163</v>
       </c>
       <c r="B4" t="n">
-        <v>91533</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128894588</v>
+        <v>128702159</v>
       </c>
       <c r="B5" t="n">
-        <v>57887</v>
+        <v>92097</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>1588</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>790319</v>
+        <v>790422</v>
       </c>
       <c r="R5" t="n">
-        <v>7366905</v>
+        <v>7366934</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1060,6 +1060,491 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128702176</v>
+      </c>
+      <c r="B6" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Norr-Lillån, Nb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>790349</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7366898</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128702175</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Norr-Lillån, Nb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>790442</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7366936</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128702158</v>
+      </c>
+      <c r="B8" t="n">
+        <v>10970</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>101449</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Olisthaerus substriatus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Paykull, 1790)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Norr-Lillån, Nb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>790368</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7366947</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Under bark på grov granlåga</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128894588</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Norr-Lillån, Nb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>790319</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7366905</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128894590</v>
+      </c>
+      <c r="B10" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Norr-Lillån, Nb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>790358</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7366800</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3922-2025 artfynd.xlsx
+++ b/artfynd/A 3922-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128702164</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128702165</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128702163</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128702159</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128702176</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128702175</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128702158</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128894588</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,8 +1590,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128894590</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 3922-2025 artfynd.xlsx
+++ b/artfynd/A 3922-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ10"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1292,27 +1292,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128702158</v>
+        <v>136483149</v>
       </c>
       <c r="B8" t="n">
-        <v>10970</v>
+        <v>79473</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>101449</v>
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Olisthaerus substriatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Paykull, 1790)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1322,13 +1327,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>790368</v>
+        <v>790399</v>
       </c>
       <c r="R8" t="n">
-        <v>7366947</v>
+        <v>7366835</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1352,17 +1357,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Under bark på grov granlåga</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1377,27 +1377,27 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Frédéric Forsmark, Sofia Åström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128702158</t>
+          <t>https://artportalen.se/Sighting/136483149</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128894588</v>
+        <v>128702158</v>
       </c>
       <c r="B9" t="n">
-        <v>58114</v>
+        <v>10970</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1405,21 +1405,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
+        <v>101449</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Olisthaerus substriatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Paykull, 1790)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1424,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>790319</v>
+        <v>790368</v>
       </c>
       <c r="R9" t="n">
-        <v>7366905</v>
+        <v>7366947</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1459,12 +1454,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Under bark på grov granlåga</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1490,38 +1490,38 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128894588</t>
+          <t>https://artportalen.se/Sighting/128702158</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128894590</v>
+        <v>128894588</v>
       </c>
       <c r="B10" t="n">
-        <v>97983</v>
+        <v>58114</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>790358</v>
+        <v>790319</v>
       </c>
       <c r="R10" t="n">
-        <v>7366800</v>
+        <v>7366905</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1591,6 +1591,108 @@
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128894588</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128894590</v>
+      </c>
+      <c r="B11" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Norr-Lillån, Nb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>790358</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7366800</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/128894590</t>
         </is>
@@ -1607,6 +1709,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3922-2025 artfynd.xlsx
+++ b/artfynd/A 3922-2025 artfynd.xlsx
@@ -1295,7 +1295,7 @@
         <v>136483149</v>
       </c>
       <c r="B8" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
